--- a/Sheet/Stage4_CubePuzzle.xlsx
+++ b/Sheet/Stage4_CubePuzzle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\Moumi_moz.A.I.c_Documents\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC49418-EA34-4AE3-8AC0-1DB6771B3F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C1744C-AE84-45E5-99E5-CB250F19B274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10065" yWindow="1275" windowWidth="21480" windowHeight="13380" activeTab="1" xr2:uid="{E4F09326-48BA-4A18-9549-0F297B741B3F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E4F09326-48BA-4A18-9549-0F297B741B3F}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="2" r:id="rId1"/>
@@ -873,15 +873,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <f ca="1">ROUND(RANDBETWEEN(-1,1),0)</f>
+        <v>-1</v>
       </c>
       <c r="E4" s="1" t="b">
-        <v>0</v>
+        <f ca="1">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <v>1</v>
       </c>
       <c r="F4" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ref="F4:G19" ca="1" si="1">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="G4" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="H4" s="1">
@@ -900,15 +904,19 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>-2</v>
+        <f t="shared" ref="D5:D68" ca="1" si="2">ROUND(RANDBETWEEN(-1,1),0)</f>
+        <v>-1</v>
       </c>
       <c r="E5" s="1" t="b">
+        <f t="shared" ref="E5:G36" ca="1" si="3">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
         <v>1</v>
       </c>
       <c r="F5" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="G5" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="H5" s="1">
@@ -927,15 +935,19 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E6" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F6" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="G6" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="H6" s="1">
@@ -954,15 +966,19 @@
         <v>4</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E7" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="F7" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="G7" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="H7" s="1">
@@ -981,15 +997,19 @@
         <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E8" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F8" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="G8" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="1">
@@ -1008,15 +1028,19 @@
         <v>6</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E9" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F9" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="G9" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="H9" s="1">
@@ -1035,16 +1059,20 @@
         <v>7</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E10" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F10" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -1062,16 +1090,20 @@
         <v>8</v>
       </c>
       <c r="D11" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="E11" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="F11" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="G11" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -1089,16 +1121,20 @@
         <v>9</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E12" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="G12" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -1116,16 +1152,20 @@
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E13" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F13" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="G13" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -1143,16 +1183,20 @@
         <v>1</v>
       </c>
       <c r="D14" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F14" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="G14" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -1170,15 +1214,19 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E15" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="H15" s="1">
@@ -1197,15 +1245,19 @@
         <v>3</v>
       </c>
       <c r="D16" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E16" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F16" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="G16" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="H16" s="1">
@@ -1224,16 +1276,20 @@
         <v>4</v>
       </c>
       <c r="D17" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E17" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F17" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1251,15 +1307,19 @@
         <v>5</v>
       </c>
       <c r="D18" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E18" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F18" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="H18" s="1">
@@ -1278,15 +1338,19 @@
         <v>6</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E19" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F19" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="G19" s="1" t="b">
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="H19" s="1">
@@ -1305,15 +1369,19 @@
         <v>7</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E20" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="F20" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="H20" s="1">
@@ -1332,16 +1400,20 @@
         <v>8</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E21" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="F21" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="G21" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -1359,15 +1431,19 @@
         <v>9</v>
       </c>
       <c r="D22" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E22" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F22" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="H22" s="1">
@@ -1386,15 +1462,19 @@
         <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E23" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F23" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="G23" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="H23" s="1">
@@ -1413,15 +1493,19 @@
         <v>1</v>
       </c>
       <c r="D24" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E24" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F24" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="G24" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="H24" s="1">
@@ -1440,15 +1524,19 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
       <c r="E25" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="F25" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="H25" s="1">
@@ -1467,15 +1555,19 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E26" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F26" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="G26" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="H26" s="1">
@@ -1494,16 +1586,20 @@
         <v>4</v>
       </c>
       <c r="D27" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E27" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F27" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="G27" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -1521,15 +1617,19 @@
         <v>5</v>
       </c>
       <c r="D28" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E28" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="F28" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="G28" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="H28" s="1">
@@ -1548,16 +1648,20 @@
         <v>6</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E29" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F29" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="G29" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -1575,16 +1679,20 @@
         <v>7</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E30" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F30" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="G30" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -1602,16 +1710,20 @@
         <v>8</v>
       </c>
       <c r="D31" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E31" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F31" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="G31" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -1629,15 +1741,19 @@
         <v>9</v>
       </c>
       <c r="D32" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E32" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F32" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="G32" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="H32" s="1">
@@ -1656,15 +1772,19 @@
         <v>0</v>
       </c>
       <c r="D33" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F33" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="G33" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="H33" s="1">
@@ -1683,16 +1803,20 @@
         <v>1</v>
       </c>
       <c r="D34" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E34" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F34" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="G34" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -1710,16 +1834,20 @@
         <v>2</v>
       </c>
       <c r="D35" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E35" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F35" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="G35" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -1737,15 +1865,19 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E36" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
       </c>
       <c r="F36" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
       <c r="G36" s="1" t="b">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="H36" s="1">
@@ -1764,15 +1896,19 @@
         <v>4</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E37" s="1" t="b">
+        <f t="shared" ref="E37:G68" ca="1" si="4">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
         <v>1</v>
       </c>
       <c r="F37" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G37" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="H37" s="1">
@@ -1791,15 +1927,19 @@
         <v>5</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E38" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F38" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="G38" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="H38" s="1">
@@ -1818,16 +1958,20 @@
         <v>6</v>
       </c>
       <c r="D39" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E39" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F39" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G39" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -1845,15 +1989,19 @@
         <v>7</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E40" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F40" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G40" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="H40" s="1">
@@ -1872,15 +2020,19 @@
         <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E41" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F41" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="G41" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="H41" s="1">
@@ -1899,16 +2051,20 @@
         <v>9</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E42" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F42" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G42" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -1926,16 +2082,20 @@
         <v>0</v>
       </c>
       <c r="D43" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E43" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F43" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G43" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -1953,16 +2113,20 @@
         <v>1</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E44" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F44" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G44" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -1980,16 +2144,20 @@
         <v>2</v>
       </c>
       <c r="D45" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E45" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F45" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G45" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -2007,15 +2175,19 @@
         <v>3</v>
       </c>
       <c r="D46" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E46" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F46" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G46" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="H46" s="1">
@@ -2034,16 +2206,20 @@
         <v>4</v>
       </c>
       <c r="D47" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E47" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F47" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G47" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -2061,16 +2237,20 @@
         <v>5</v>
       </c>
       <c r="D48" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E48" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F48" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="G48" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -2088,15 +2268,19 @@
         <v>6</v>
       </c>
       <c r="D49" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
       <c r="E49" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F49" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G49" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="H49" s="1">
@@ -2115,15 +2299,19 @@
         <v>7</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E50" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F50" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G50" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="H50" s="1">
@@ -2142,16 +2330,20 @@
         <v>8</v>
       </c>
       <c r="D51" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E51" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="F51" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G51" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -2169,16 +2361,20 @@
         <v>9</v>
       </c>
       <c r="D52" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E52" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F52" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G52" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -2196,16 +2392,20 @@
         <v>0</v>
       </c>
       <c r="D53" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E53" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F53" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G53" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -2223,16 +2423,20 @@
         <v>1</v>
       </c>
       <c r="D54" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="E54" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F54" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G54" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -2250,15 +2454,19 @@
         <v>2</v>
       </c>
       <c r="D55" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F55" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G55" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="H55" s="1">
@@ -2277,16 +2485,20 @@
         <v>3</v>
       </c>
       <c r="D56" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
       <c r="E56" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="F56" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G56" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -2304,16 +2516,20 @@
         <v>4</v>
       </c>
       <c r="D57" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>-1</v>
       </c>
       <c r="E57" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F57" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G57" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -2331,15 +2547,19 @@
         <v>5</v>
       </c>
       <c r="D58" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
       <c r="E58" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F58" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G58" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="H58" s="1">
@@ -2358,16 +2578,20 @@
         <v>6</v>
       </c>
       <c r="D59" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>-1</v>
       </c>
       <c r="E59" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F59" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G59" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -2385,16 +2609,20 @@
         <v>7</v>
       </c>
       <c r="D60" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="E60" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F60" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="G60" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -2412,15 +2640,19 @@
         <v>8</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E61" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F61" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G61" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="H61" s="1">
@@ -2439,16 +2671,20 @@
         <v>9</v>
       </c>
       <c r="D62" s="1">
+        <f t="shared" ca="1" si="2"/>
         <v>-1</v>
       </c>
       <c r="E62" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F62" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="G62" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -2466,15 +2702,19 @@
         <v>0</v>
       </c>
       <c r="D63" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E63" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="F63" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G63" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="H63" s="1">
@@ -2493,16 +2733,20 @@
         <v>1</v>
       </c>
       <c r="D64" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E64" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F64" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="G64" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -2520,16 +2764,20 @@
         <v>2</v>
       </c>
       <c r="D65" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E65" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="F65" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G65" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -2547,16 +2795,20 @@
         <v>3</v>
       </c>
       <c r="D66" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="E66" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F66" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="G66" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -2574,16 +2826,20 @@
         <v>4</v>
       </c>
       <c r="D67" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
       </c>
       <c r="E67" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F67" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G67" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -2601,16 +2857,20 @@
         <v>5</v>
       </c>
       <c r="D68" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
       </c>
       <c r="E68" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F68" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="G68" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -2628,16 +2888,20 @@
         <v>6</v>
       </c>
       <c r="D69" s="1">
+        <f t="shared" ref="D69:D101" ca="1" si="5">ROUND(RANDBETWEEN(-1,1),0)</f>
         <v>0</v>
       </c>
       <c r="E69" s="1" t="b">
+        <f t="shared" ref="E69:G101" ca="1" si="6">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
         <v>1</v>
       </c>
       <c r="F69" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G69" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -2655,15 +2919,19 @@
         <v>7</v>
       </c>
       <c r="D70" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="E70" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F70" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G70" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H70" s="1">
@@ -2682,16 +2950,20 @@
         <v>8</v>
       </c>
       <c r="D71" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E71" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F71" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G71" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -2709,15 +2981,19 @@
         <v>9</v>
       </c>
       <c r="D72" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E72" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="F72" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G72" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="H72" s="1">
@@ -2736,16 +3012,20 @@
         <v>0</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="E73" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F73" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="G73" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -2763,16 +3043,20 @@
         <v>1</v>
       </c>
       <c r="D74" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="E74" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F74" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G74" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -2790,15 +3074,19 @@
         <v>2</v>
       </c>
       <c r="D75" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E75" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="F75" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="G75" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H75" s="1">
@@ -2817,15 +3105,19 @@
         <v>3</v>
       </c>
       <c r="D76" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E76" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F76" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G76" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="H76" s="1">
@@ -2844,16 +3136,20 @@
         <v>4</v>
       </c>
       <c r="D77" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E77" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F77" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G77" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -2871,16 +3167,20 @@
         <v>5</v>
       </c>
       <c r="D78" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E78" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F78" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G78" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
@@ -2898,15 +3198,19 @@
         <v>6</v>
       </c>
       <c r="D79" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E79" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F79" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="G79" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H79" s="1">
@@ -2925,15 +3229,19 @@
         <v>7</v>
       </c>
       <c r="D80" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="E80" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F80" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="G80" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H80" s="1">
@@ -2952,16 +3260,20 @@
         <v>8</v>
       </c>
       <c r="D81" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E81" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="F81" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G81" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -2979,16 +3291,20 @@
         <v>9</v>
       </c>
       <c r="D82" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E82" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F82" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="G82" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -3006,15 +3322,19 @@
         <v>0</v>
       </c>
       <c r="D83" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E83" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="F83" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G83" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="H83" s="1">
@@ -3033,15 +3353,19 @@
         <v>1</v>
       </c>
       <c r="D84" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="E84" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F84" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G84" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="H84" s="1">
@@ -3060,16 +3384,20 @@
         <v>2</v>
       </c>
       <c r="D85" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="E85" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F85" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="G85" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -3087,15 +3415,19 @@
         <v>3</v>
       </c>
       <c r="D86" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E86" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="F86" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G86" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="H86" s="1">
@@ -3114,16 +3446,20 @@
         <v>4</v>
       </c>
       <c r="D87" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E87" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F87" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G87" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -3141,15 +3477,19 @@
         <v>5</v>
       </c>
       <c r="D88" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E88" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F88" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G88" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H88" s="1">
@@ -3168,16 +3508,20 @@
         <v>6</v>
       </c>
       <c r="D89" s="1">
-        <v>-1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E89" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F89" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G89" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -3195,16 +3539,20 @@
         <v>7</v>
       </c>
       <c r="D90" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E90" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="F90" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="G90" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -3222,15 +3570,19 @@
         <v>8</v>
       </c>
       <c r="D91" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="E91" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F91" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G91" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="H91" s="1">
@@ -3249,16 +3601,20 @@
         <v>9</v>
       </c>
       <c r="D92" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>-1</v>
       </c>
       <c r="E92" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="F92" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="G92" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -3276,15 +3632,19 @@
         <v>0</v>
       </c>
       <c r="D93" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E93" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="F93" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="G93" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="H93" s="1">
@@ -3303,16 +3663,20 @@
         <v>1</v>
       </c>
       <c r="D94" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E94" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F94" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G94" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -3330,15 +3694,19 @@
         <v>2</v>
       </c>
       <c r="D95" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>-1</v>
       </c>
       <c r="E95" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F95" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G95" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H95" s="1">
@@ -3357,16 +3725,20 @@
         <v>3</v>
       </c>
       <c r="D96" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E96" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="F96" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="G96" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -3384,16 +3756,20 @@
         <v>4</v>
       </c>
       <c r="D97" s="1">
-        <v>-2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E97" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F97" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="G97" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -3411,16 +3787,20 @@
         <v>5</v>
       </c>
       <c r="D98" s="1">
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E98" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="F98" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G98" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -3438,15 +3818,19 @@
         <v>6</v>
       </c>
       <c r="D99" s="1">
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E99" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="F99" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="G99" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H99" s="1">
@@ -3465,16 +3849,20 @@
         <v>7</v>
       </c>
       <c r="D100" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E100" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="F100" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G100" s="1" t="b">
-        <v>1</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -3492,16 +3880,20 @@
         <v>8</v>
       </c>
       <c r="D101" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E101" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="F101" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
       <c r="G101" s="1" t="b">
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>

--- a/Sheet/Stage4_CubePuzzle.xlsx
+++ b/Sheet/Stage4_CubePuzzle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\Moumi_moz.A.I.c_Documents\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C1744C-AE84-45E5-99E5-CB250F19B274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22C3BE0-F0E6-4FA0-86C3-74770B5D313C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E4F09326-48BA-4A18-9549-0F297B741B3F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E4F09326-48BA-4A18-9549-0F297B741B3F}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="2" r:id="rId1"/>
@@ -39,24 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
   <si>
     <t>ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>height</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>place_z</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>place_x</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -164,10 +152,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>각 발판의 높이 값 (y 좌표)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>color</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -176,16 +160,77 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>각 발판의 색상 값 (r, g, b 키)</t>
+    <t>near</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>row</t>
+  </si>
+  <si>
+    <t>posX</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>otherSwitch</t>
+    <t>posY</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>각 발판에 추가로 배치되는 스위치 개수
-* 기본 1개에 더해져 총 otherSwitch+1개의 스위치가 배치됨</t>
+    <t>switchCondition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>switchValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>near</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>row</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 발판의 스위치 작동 시 함께 색상이 변경되는 큐브 조건</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 발판의 스위치 작동 시 변경되는 색상 키
+* 1 = r / 2 = g / 4 = b 키로 지정하여 비트 합으로 입력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 발판의 초기 색상 값 (r, g, b 키)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전후좌우 1칸씩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 가로줄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 세로줄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 현재 색상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>column</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -697,24 +742,24 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
@@ -779,33 +824,34 @@
   <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="7" max="7" width="13.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -813,30 +859,29 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <f>B3*10+C3</f>
         <v>0</v>
       </c>
       <c r="B3" s="1">
@@ -845,8 +890,8 @@
       <c r="C3" s="1">
         <v>0</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
+      <c r="D3" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="b">
         <v>1</v>
@@ -854,8 +899,8 @@
       <c r="F3" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="1" t="b">
-        <v>1</v>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -863,7 +908,6 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A102" si="0">B4*10+C4</f>
         <v>1</v>
       </c>
       <c r="B4" s="1">
@@ -872,29 +916,25 @@
       <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
-        <f ca="1">ROUND(RANDBETWEEN(-1,1),0)</f>
-        <v>-1</v>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="b">
-        <f ca="1">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
         <v>1</v>
       </c>
       <c r="F4" s="1" t="b">
-        <f t="shared" ref="F4:G19" ca="1" si="1">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <f t="shared" ref="H4" ca="1" si="0">ROUNDDOWN(RAND()*7,0)+1</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -903,29 +943,29 @@
       <c r="C5" s="1">
         <v>2</v>
       </c>
-      <c r="D5" s="1">
-        <f t="shared" ref="D5:D68" ca="1" si="2">ROUND(RANDBETWEEN(-1,1),0)</f>
-        <v>-1</v>
+      <c r="D5" s="1" t="b">
+        <f ca="1">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="b">
-        <f t="shared" ref="E5:G36" ca="1" si="3">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
-        <v>1</v>
+        <f t="shared" ref="E5:F12" ca="1" si="1">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <f ca="1">ROUNDDOWN(RAND()*7,0)+1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -934,29 +974,29 @@
       <c r="C6" s="1">
         <v>3</v>
       </c>
-      <c r="D6" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D6" s="1" t="b">
+        <f t="shared" ref="D6:D12" ca="1" si="2">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+      <c r="G6" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <f t="shared" ref="H6:H69" ca="1" si="3">ROUNDDOWN(RAND()*7,0)+1</f>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -965,29 +1005,29 @@
       <c r="C7" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="b">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="F7" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -996,29 +1036,29 @@
       <c r="C8" s="1">
         <v>5</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="b">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="F8" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -1027,29 +1067,29 @@
       <c r="C9" s="1">
         <v>6</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="b">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+      <c r="G9" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -1058,29 +1098,29 @@
       <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="b">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="G10" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+      <c r="G10" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -1089,29 +1129,29 @@
       <c r="C11" s="1">
         <v>8</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="1" t="b">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="F11" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -1120,29 +1160,29 @@
       <c r="C12" s="1">
         <v>9</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="1" t="b">
         <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
       <c r="E12" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="F12" s="1" t="b">
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="G12" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+      <c r="G12" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -1151,29 +1191,25 @@
       <c r="C13" s="1">
         <v>0</v>
       </c>
-      <c r="D13" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D13" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E13" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
       <c r="F13" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -1182,29 +1218,25 @@
       <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D14" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+      <c r="D14" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E14" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G14" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -1213,29 +1245,29 @@
       <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="D15" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D15" s="1" t="b">
+        <f t="shared" ref="D15:F46" ca="1" si="4">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E15" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F15" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -1244,29 +1276,29 @@
       <c r="C16" s="1">
         <v>3</v>
       </c>
-      <c r="D16" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D16" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="E16" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F16" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G16" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -1275,29 +1307,29 @@
       <c r="C17" s="1">
         <v>4</v>
       </c>
-      <c r="D17" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+      <c r="D17" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="E17" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F17" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G17" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -1306,29 +1338,29 @@
       <c r="C18" s="1">
         <v>5</v>
       </c>
-      <c r="D18" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D18" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F18" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -1337,29 +1369,29 @@
       <c r="C19" s="1">
         <v>6</v>
       </c>
-      <c r="D19" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D19" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E19" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F19" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G19" s="1" t="b">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -1368,29 +1400,29 @@
       <c r="C20" s="1">
         <v>7</v>
       </c>
-      <c r="D20" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+      <c r="D20" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F20" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -1399,29 +1431,29 @@
       <c r="C21" s="1">
         <v>8</v>
       </c>
-      <c r="D21" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D21" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E21" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F21" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -1430,29 +1462,29 @@
       <c r="C22" s="1">
         <v>9</v>
       </c>
-      <c r="D22" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+      <c r="D22" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="E22" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F22" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -1461,29 +1493,29 @@
       <c r="C23" s="1">
         <v>0</v>
       </c>
-      <c r="D23" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D23" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F23" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -1492,29 +1524,29 @@
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D24" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E24" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F24" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -1523,29 +1555,29 @@
       <c r="C25" s="1">
         <v>2</v>
       </c>
-      <c r="D25" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D25" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E25" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="F25" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -1554,29 +1586,29 @@
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D26" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E26" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F26" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G26" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -1585,29 +1617,29 @@
       <c r="C27" s="1">
         <v>4</v>
       </c>
-      <c r="D27" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D27" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="E27" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F27" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G27" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -1616,29 +1648,29 @@
       <c r="C28" s="1">
         <v>5</v>
       </c>
-      <c r="D28" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D28" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E28" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F28" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -1647,29 +1679,29 @@
       <c r="C29" s="1">
         <v>6</v>
       </c>
-      <c r="D29" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D29" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E29" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="F29" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -1678,29 +1710,29 @@
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D30" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E30" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -1709,29 +1741,29 @@
       <c r="C31" s="1">
         <v>8</v>
       </c>
-      <c r="D31" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D31" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="E31" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F31" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B32" s="1">
@@ -1740,29 +1772,29 @@
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D32" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E32" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F32" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B33" s="1">
@@ -1771,29 +1803,29 @@
       <c r="C33" s="1">
         <v>0</v>
       </c>
-      <c r="D33" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D33" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E33" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="F33" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B34" s="1">
@@ -1802,29 +1834,29 @@
       <c r="C34" s="1">
         <v>1</v>
       </c>
-      <c r="D34" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D34" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="E34" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F34" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B35" s="1">
@@ -1833,29 +1865,29 @@
       <c r="C35" s="1">
         <v>2</v>
       </c>
-      <c r="D35" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D35" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E35" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="F35" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B36" s="1">
@@ -1864,29 +1896,29 @@
       <c r="C36" s="1">
         <v>3</v>
       </c>
-      <c r="D36" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D36" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E36" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="F36" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G36" s="1" t="b">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B37" s="1">
@@ -1895,29 +1927,29 @@
       <c r="C37" s="1">
         <v>4</v>
       </c>
-      <c r="D37" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D37" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="b">
-        <f t="shared" ref="E37:G68" ca="1" si="4">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="F37" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="G37" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+      <c r="G37" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B38" s="1">
@@ -1926,29 +1958,29 @@
       <c r="C38" s="1">
         <v>5</v>
       </c>
-      <c r="D38" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D38" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E38" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G38" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B39" s="1">
@@ -1957,29 +1989,29 @@
       <c r="C39" s="1">
         <v>6</v>
       </c>
-      <c r="D39" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D39" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E39" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G39" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B40" s="1">
@@ -1988,29 +2020,29 @@
       <c r="C40" s="1">
         <v>7</v>
       </c>
-      <c r="D40" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+      <c r="D40" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="E40" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
-      <c r="G40" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+      <c r="G40" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B41" s="1">
@@ -2019,9 +2051,9 @@
       <c r="C41" s="1">
         <v>8</v>
       </c>
-      <c r="D41" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D41" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="E41" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
@@ -2029,19 +2061,19 @@
       </c>
       <c r="F41" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G41" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B42" s="1">
@@ -2050,29 +2082,29 @@
       <c r="C42" s="1">
         <v>9</v>
       </c>
-      <c r="D42" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D42" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E42" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G42" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B43" s="1">
@@ -2081,29 +2113,29 @@
       <c r="C43" s="1">
         <v>0</v>
       </c>
-      <c r="D43" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D43" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="E43" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B44" s="1">
@@ -2112,9 +2144,9 @@
       <c r="C44" s="1">
         <v>1</v>
       </c>
-      <c r="D44" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D44" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="E44" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
@@ -2122,19 +2154,19 @@
       </c>
       <c r="F44" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G44" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G44" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B45" s="1">
@@ -2143,29 +2175,29 @@
       <c r="C45" s="1">
         <v>2</v>
       </c>
-      <c r="D45" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D45" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="E45" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="G45" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+      <c r="G45" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B46" s="1">
@@ -2174,29 +2206,29 @@
       <c r="C46" s="1">
         <v>3</v>
       </c>
-      <c r="D46" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D46" s="1" t="b">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="1" t="b">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G46" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B47" s="1">
@@ -2205,29 +2237,29 @@
       <c r="C47" s="1">
         <v>4</v>
       </c>
-      <c r="D47" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D47" s="1" t="b">
+        <f t="shared" ref="D47:F78" ca="1" si="5">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <v>1</v>
       </c>
       <c r="E47" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F47" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B48" s="1">
@@ -2236,29 +2268,29 @@
       <c r="C48" s="1">
         <v>5</v>
       </c>
-      <c r="D48" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D48" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E48" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G48" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B49" s="1">
@@ -2267,29 +2299,29 @@
       <c r="C49" s="1">
         <v>6</v>
       </c>
-      <c r="D49" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D49" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E49" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F49" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G49" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G49" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B50" s="1">
@@ -2298,29 +2330,29 @@
       <c r="C50" s="1">
         <v>7</v>
       </c>
-      <c r="D50" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D50" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E50" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="F50" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B51" s="1">
@@ -2329,29 +2361,29 @@
       <c r="C51" s="1">
         <v>8</v>
       </c>
-      <c r="D51" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D51" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E51" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="F51" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B52" s="1">
@@ -2360,29 +2392,29 @@
       <c r="C52" s="1">
         <v>9</v>
       </c>
-      <c r="D52" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D52" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E52" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="F52" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B53" s="1">
@@ -2391,29 +2423,29 @@
       <c r="C53" s="1">
         <v>0</v>
       </c>
-      <c r="D53" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D53" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E53" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="F53" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G53" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B54" s="1">
@@ -2422,29 +2454,29 @@
       <c r="C54" s="1">
         <v>1</v>
       </c>
-      <c r="D54" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+      <c r="D54" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E54" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F54" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B55" s="1">
@@ -2453,29 +2485,29 @@
       <c r="C55" s="1">
         <v>2</v>
       </c>
-      <c r="D55" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D55" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E55" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F55" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G55" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B56" s="1">
@@ -2484,29 +2516,29 @@
       <c r="C56" s="1">
         <v>3</v>
       </c>
-      <c r="D56" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+      <c r="D56" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E56" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="F56" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G56" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B57" s="1">
@@ -2515,29 +2547,29 @@
       <c r="C57" s="1">
         <v>4</v>
       </c>
-      <c r="D57" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D57" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E57" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="F57" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G57" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G57" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B58" s="1">
@@ -2546,29 +2578,29 @@
       <c r="C58" s="1">
         <v>5</v>
       </c>
-      <c r="D58" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D58" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E58" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F58" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G58" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B59" s="1">
@@ -2577,29 +2609,29 @@
       <c r="C59" s="1">
         <v>6</v>
       </c>
-      <c r="D59" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D59" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E59" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F59" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B60" s="1">
@@ -2608,29 +2640,29 @@
       <c r="C60" s="1">
         <v>7</v>
       </c>
-      <c r="D60" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D60" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E60" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="F60" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G60" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B61" s="1">
@@ -2639,29 +2671,29 @@
       <c r="C61" s="1">
         <v>8</v>
       </c>
-      <c r="D61" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D61" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E61" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="F61" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G61" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G61" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B62" s="1">
@@ -2670,29 +2702,29 @@
       <c r="C62" s="1">
         <v>9</v>
       </c>
-      <c r="D62" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D62" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="F62" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G62" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B63" s="1">
@@ -2701,29 +2733,29 @@
       <c r="C63" s="1">
         <v>0</v>
       </c>
-      <c r="D63" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D63" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E63" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="F63" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G63" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B64" s="1">
@@ -2732,29 +2764,29 @@
       <c r="C64" s="1">
         <v>1</v>
       </c>
-      <c r="D64" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+      <c r="D64" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E64" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="F64" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B65" s="1">
@@ -2763,29 +2795,29 @@
       <c r="C65" s="1">
         <v>2</v>
       </c>
-      <c r="D65" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D65" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E65" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="F65" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G65" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H65" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B66" s="1">
@@ -2794,29 +2826,29 @@
       <c r="C66" s="1">
         <v>3</v>
       </c>
-      <c r="D66" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D66" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E66" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="F66" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G66" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
       </c>
       <c r="H66" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B67" s="1">
@@ -2825,29 +2857,29 @@
       <c r="C67" s="1">
         <v>4</v>
       </c>
-      <c r="D67" s="1">
-        <f t="shared" ca="1" si="2"/>
+      <c r="D67" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E67" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F67" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G67" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G67" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B68" s="1">
@@ -2856,29 +2888,29 @@
       <c r="C68" s="1">
         <v>5</v>
       </c>
-      <c r="D68" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+      <c r="D68" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E68" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F68" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G68" s="1" t="b">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G68" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B69" s="1">
@@ -2887,29 +2919,29 @@
       <c r="C69" s="1">
         <v>6</v>
       </c>
-      <c r="D69" s="1">
-        <f t="shared" ref="D69:D101" ca="1" si="5">ROUND(RANDBETWEEN(-1,1),0)</f>
+      <c r="D69" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E69" s="1" t="b">
-        <f t="shared" ref="E69:G101" ca="1" si="6">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="F69" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G69" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="B70" s="1">
@@ -2918,29 +2950,29 @@
       <c r="C70" s="1">
         <v>7</v>
       </c>
-      <c r="D70" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D70" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E70" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="F70" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G70" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G70" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <f t="shared" ref="H70:H101" ca="1" si="6">ROUNDDOWN(RAND()*7,0)+1</f>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="B71" s="1">
@@ -2949,29 +2981,29 @@
       <c r="C71" s="1">
         <v>8</v>
       </c>
-      <c r="D71" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+      <c r="D71" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E71" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F71" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
+      </c>
+      <c r="H71" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F71" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="B72" s="1">
@@ -2980,29 +3012,29 @@
       <c r="C72" s="1">
         <v>9</v>
       </c>
-      <c r="D72" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+      <c r="D72" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E72" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G72" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H72" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F72" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G72" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H72" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="B73" s="1">
@@ -3011,29 +3043,29 @@
       <c r="C73" s="1">
         <v>0</v>
       </c>
-      <c r="D73" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D73" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E73" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G73" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H73" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F73" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G73" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="B74" s="1">
@@ -3042,29 +3074,29 @@
       <c r="C74" s="1">
         <v>1</v>
       </c>
-      <c r="D74" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D74" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="E74" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
+      </c>
+      <c r="H74" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G74" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H74" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="B75" s="1">
@@ -3073,29 +3105,29 @@
       <c r="C75" s="1">
         <v>2</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="1" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="E75" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F75" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
+      </c>
+      <c r="H75" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F75" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G75" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="B76" s="1">
@@ -3104,29 +3136,29 @@
       <c r="C76" s="1">
         <v>3</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="1" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="E76" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F76" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
+      </c>
+      <c r="H76" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F76" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G76" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H76" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="B77" s="1">
@@ -3135,29 +3167,29 @@
       <c r="C77" s="1">
         <v>4</v>
       </c>
-      <c r="D77" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+      <c r="D77" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E77" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G77" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
+      </c>
+      <c r="H77" s="1">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
-      </c>
-      <c r="F77" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G77" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="B78" s="1">
@@ -3166,29 +3198,29 @@
       <c r="C78" s="1">
         <v>5</v>
       </c>
-      <c r="D78" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+      <c r="D78" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
       </c>
       <c r="E78" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F78" s="1" t="b">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G78" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
+      </c>
+      <c r="H78" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F78" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="B79" s="1">
@@ -3197,29 +3229,29 @@
       <c r="C79" s="1">
         <v>6</v>
       </c>
-      <c r="D79" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D79" s="1" t="b">
+        <f t="shared" ref="D79:F101" ca="1" si="7">IF(RAND()&gt;=0.5,TRUE,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E79" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G79" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
+      </c>
+      <c r="H79" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G79" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="B80" s="1">
@@ -3228,29 +3260,29 @@
       <c r="C80" s="1">
         <v>7</v>
       </c>
-      <c r="D80" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D80" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E80" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F80" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G80" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H80" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F80" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G80" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="B81" s="1">
@@ -3259,29 +3291,29 @@
       <c r="C81" s="1">
         <v>8</v>
       </c>
-      <c r="D81" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+      <c r="D81" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E81" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G81" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
+      </c>
+      <c r="H81" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F81" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G81" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="B82" s="1">
@@ -3290,29 +3322,29 @@
       <c r="C82" s="1">
         <v>9</v>
       </c>
-      <c r="D82" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D82" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="E82" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G82" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
+      </c>
+      <c r="H82" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F82" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G82" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H82" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="B83" s="1">
@@ -3321,29 +3353,29 @@
       <c r="C83" s="1">
         <v>0</v>
       </c>
-      <c r="D83" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D83" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="E83" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F83" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
+      </c>
+      <c r="H83" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G83" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H83" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="B84" s="1">
@@ -3352,29 +3384,29 @@
       <c r="C84" s="1">
         <v>1</v>
       </c>
-      <c r="D84" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D84" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E84" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F84" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G84" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H84" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F84" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G84" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H84" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <f t="shared" si="0"/>
         <v>82</v>
       </c>
       <c r="B85" s="1">
@@ -3383,29 +3415,29 @@
       <c r="C85" s="1">
         <v>2</v>
       </c>
-      <c r="D85" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D85" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E85" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F85" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
+      </c>
+      <c r="H85" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="B86" s="1">
@@ -3414,29 +3446,29 @@
       <c r="C86" s="1">
         <v>3</v>
       </c>
-      <c r="D86" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+      <c r="D86" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E86" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F86" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H86" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F86" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G86" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H86" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="B87" s="1">
@@ -3445,29 +3477,29 @@
       <c r="C87" s="1">
         <v>4</v>
       </c>
-      <c r="D87" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+      <c r="D87" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E87" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F87" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
+      </c>
+      <c r="H87" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F87" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G87" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H87" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="B88" s="1">
@@ -3476,29 +3508,29 @@
       <c r="C88" s="1">
         <v>5</v>
       </c>
-      <c r="D88" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D88" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="E88" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F88" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G88" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
+      </c>
+      <c r="H88" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F88" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G88" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H88" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="B89" s="1">
@@ -3507,29 +3539,29 @@
       <c r="C89" s="1">
         <v>6</v>
       </c>
-      <c r="D89" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+      <c r="D89" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
       </c>
       <c r="E89" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G89" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
+      </c>
+      <c r="H89" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F89" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G89" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H89" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="B90" s="1">
@@ -3538,29 +3570,29 @@
       <c r="C90" s="1">
         <v>7</v>
       </c>
-      <c r="D90" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D90" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="E90" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
+      </c>
+      <c r="H90" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F90" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G90" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H90" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <f t="shared" si="0"/>
         <v>88</v>
       </c>
       <c r="B91" s="1">
@@ -3569,29 +3601,29 @@
       <c r="C91" s="1">
         <v>8</v>
       </c>
-      <c r="D91" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D91" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E91" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F91" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G91" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H91" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F91" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G91" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H91" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="B92" s="1">
@@ -3600,29 +3632,29 @@
       <c r="C92" s="1">
         <v>9</v>
       </c>
-      <c r="D92" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D92" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E92" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G92" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H92" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F92" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G92" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H92" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="B93" s="1">
@@ -3631,29 +3663,29 @@
       <c r="C93" s="1">
         <v>0</v>
       </c>
-      <c r="D93" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D93" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="E93" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F93" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>color</v>
+      </c>
+      <c r="H93" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F93" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G93" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="B94" s="1">
@@ -3662,29 +3694,29 @@
       <c r="C94" s="1">
         <v>1</v>
       </c>
-      <c r="D94" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+      <c r="D94" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
       </c>
       <c r="E94" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F94" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H94" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F94" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G94" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H94" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="B95" s="1">
@@ -3693,29 +3725,29 @@
       <c r="C95" s="1">
         <v>2</v>
       </c>
-      <c r="D95" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>-1</v>
+      <c r="D95" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
       </c>
       <c r="E95" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F95" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G95" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>column</v>
+      </c>
+      <c r="H95" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F95" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G95" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H95" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="B96" s="1">
@@ -3724,29 +3756,29 @@
       <c r="C96" s="1">
         <v>3</v>
       </c>
-      <c r="D96" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D96" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="E96" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F96" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H96" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F96" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G96" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H96" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="B97" s="1">
@@ -3755,29 +3787,29 @@
       <c r="C97" s="1">
         <v>4</v>
       </c>
-      <c r="D97" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+      <c r="D97" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E97" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F97" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G97" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H97" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F97" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G97" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="B98" s="1">
@@ -3786,29 +3818,29 @@
       <c r="C98" s="1">
         <v>5</v>
       </c>
-      <c r="D98" s="1">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+      <c r="D98" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
       </c>
       <c r="E98" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F98" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G98" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
+      </c>
+      <c r="H98" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F98" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G98" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="B99" s="1">
@@ -3817,29 +3849,29 @@
       <c r="C99" s="1">
         <v>6</v>
       </c>
-      <c r="D99" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D99" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
       <c r="E99" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H99" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F99" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G99" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H99" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="B100" s="1">
@@ -3848,29 +3880,29 @@
       <c r="C100" s="1">
         <v>7</v>
       </c>
-      <c r="D100" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D100" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="E100" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G100" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>near</v>
+      </c>
+      <c r="H100" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F100" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G100" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H100" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <f t="shared" si="0"/>
         <v>98</v>
       </c>
       <c r="B101" s="1">
@@ -3879,29 +3911,29 @@
       <c r="C101" s="1">
         <v>8</v>
       </c>
-      <c r="D101" s="1">
-        <f t="shared" ca="1" si="5"/>
+      <c r="D101" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="E101" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F101" s="1" t="b">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G101" s="1" t="str">
+        <f ca="1">VLOOKUP(ROUNDDOWN(RAND()*4,0),Index!$C$13:$E$16,2,FALSE)</f>
+        <v>row</v>
+      </c>
+      <c r="H101" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F101" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G101" s="1" t="b">
-        <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H101" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="B102" s="1">
@@ -3910,8 +3942,8 @@
       <c r="C102" s="1">
         <v>9</v>
       </c>
-      <c r="D102" s="1">
-        <v>0</v>
+      <c r="D102" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E102" s="1" t="b">
         <v>1</v>
@@ -3919,8 +3951,8 @@
       <c r="F102" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G102" s="1" t="b">
-        <v>1</v>
+      <c r="G102" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -3938,7 +3970,7 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="B2:E10"/>
+  <dimension ref="B2:E16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
@@ -3950,36 +3982,36 @@
   <sheetData>
     <row r="2" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B2" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -3990,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -4001,13 +4033,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -4015,13 +4047,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -4029,13 +4061,13 @@
         <v>4</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="27" x14ac:dyDescent="0.3">
@@ -4043,13 +4075,68 @@
         <v>5</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C14" s="8">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C15" s="8">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C16" s="8">
+        <v>3</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
